--- a/Practical3/Excel Sheets/STM32F0_Task4_Data.xlsx
+++ b/Practical3/Excel Sheets/STM32F0_Task4_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/ngrmar007_myuct_ac_za/Documents/Third Year/EEE3096s-repository/EEE3096S-Group-39/Practical3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/ngrmar007_myuct_ac_za/Documents/Third Year/EEE3096s-repository/EEE3096S-Group-39/Practical3/Excel Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{D388F7E4-975B-476E-8D73-7F6731EF7515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="84" yWindow="0" windowWidth="10896" windowHeight="10008" xr2:uid="{4D7707D8-D18D-44FF-AC6F-D204C547A644}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4D7707D8-D18D-44FF-AC6F-D204C547A644}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
